--- a/DN - Java FSE Mandatory hands-on detail (1).xlsx
+++ b/DN - Java FSE Mandatory hands-on detail (1).xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/239914_cognizant_com/Documents/2025/Academy work/Digital Nurture/DN 5.0/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PAT_Notes\Placements\Cognizant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{38815D58-CAD9-44C0-B366-FB59C6453CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A83D4995-9CD0-446A-9BFE-55A9EAB2B518}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E078EC40-2268-4F4F-B14B-9403122955B8}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305"/>
   </bookViews>
   <sheets>
     <sheet name="Java FSE" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -320,8 +319,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -475,14 +474,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -495,16 +504,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -838,32 +837,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57EFDF7-9EDE-4E32-9B50-93240323B319}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="23.08984375" customWidth="1"/>
-    <col min="2" max="2" width="22.6328125" customWidth="1"/>
-    <col min="3" max="3" width="47.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.26953125" customWidth="1"/>
-    <col min="5" max="5" width="30.453125" customWidth="1"/>
+    <col min="1" max="1" width="23.125" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="47.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.25" customWidth="1"/>
+    <col min="5" max="5" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="15">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="13" t="s">
+      <c r="C1" s="16"/>
+      <c r="D1" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="14"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="16"/>
+      <c r="E1" s="18"/>
+    </row>
+    <row r="2" spans="1:5" ht="15">
+      <c r="A2" s="10"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -877,7 +876,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="28.5">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -890,7 +889,7 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="28.5">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -903,7 +902,7 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="28.5">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -916,7 +915,7 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="28.5">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -929,7 +928,7 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -942,7 +941,7 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -955,7 +954,7 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="28.5">
       <c r="A9" s="4" t="s">
         <v>14</v>
       </c>
@@ -968,7 +967,7 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="28.5">
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
@@ -981,29 +980,29 @@
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:5" ht="28.5">
+      <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="13" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="10"/>
-      <c r="B12" s="8"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="12"/>
+      <c r="B12" s="14"/>
       <c r="C12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-    </row>
-    <row r="13" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+    </row>
+    <row r="13" spans="1:5" ht="28.5">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
@@ -1016,7 +1015,7 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="28.5">
       <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
@@ -1029,7 +1028,7 @@
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
@@ -1042,7 +1041,7 @@
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="28.5">
       <c r="A16" s="4" t="s">
         <v>26</v>
       </c>
@@ -1057,7 +1056,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="28.5">
       <c r="A17" s="4" t="s">
         <v>26</v>
       </c>
@@ -1072,7 +1071,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="28.5">
       <c r="A18" s="4" t="s">
         <v>26</v>
       </c>
@@ -1087,7 +1086,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="28.5">
       <c r="A19" s="4" t="s">
         <v>34</v>
       </c>
@@ -1104,7 +1103,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="28.5">
       <c r="A20" s="4" t="s">
         <v>34</v>
       </c>
@@ -1121,7 +1120,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="28.5">
       <c r="A21" s="4" t="s">
         <v>34</v>
       </c>
@@ -1134,7 +1133,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="42.75">
       <c r="A22" s="4" t="s">
         <v>34</v>
       </c>
@@ -1147,7 +1146,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="28.5">
       <c r="A23" s="4" t="s">
         <v>34</v>
       </c>
@@ -1160,7 +1159,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="28.5">
       <c r="A24" s="4" t="s">
         <v>34</v>
       </c>
@@ -1173,7 +1172,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="28.5">
       <c r="A25" s="4" t="s">
         <v>46</v>
       </c>
@@ -1190,7 +1189,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="28.5">
       <c r="A26" s="4" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1202,7 @@
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
     </row>
-    <row r="27" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="28.5">
       <c r="A27" s="4" t="s">
         <v>46</v>
       </c>
@@ -1216,7 +1215,7 @@
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
     </row>
-    <row r="28" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="28.5">
       <c r="A28" s="4" t="s">
         <v>46</v>
       </c>
@@ -1229,7 +1228,7 @@
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
     </row>
-    <row r="29" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="28.5">
       <c r="A29" s="4" t="s">
         <v>46</v>
       </c>
@@ -1242,7 +1241,7 @@
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
     </row>
-    <row r="30" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="28.5">
       <c r="A30" s="4" t="s">
         <v>46</v>
       </c>
@@ -1255,33 +1254,33 @@
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A31" s="9" t="s">
+    <row r="31" spans="1:5" ht="28.5">
+      <c r="A31" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="11" t="s">
         <v>59</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="10"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="10"/>
+    <row r="32" spans="1:5">
+      <c r="A32" s="12"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="12"/>
       <c r="E32" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5">
       <c r="A33" s="4" t="s">
         <v>63</v>
       </c>
@@ -1298,7 +1297,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5">
       <c r="A34" s="4" t="s">
         <v>63</v>
       </c>
@@ -1315,7 +1314,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5">
       <c r="A35" s="4" t="s">
         <v>63</v>
       </c>
@@ -1332,7 +1331,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5">
       <c r="A36" s="4" t="s">
         <v>63</v>
       </c>
@@ -1345,7 +1344,7 @@
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5">
       <c r="A37" s="4" t="s">
         <v>63</v>
       </c>
@@ -1358,7 +1357,7 @@
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>63</v>
       </c>
@@ -1375,7 +1374,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5">
       <c r="A39" s="4" t="s">
         <v>63</v>
       </c>
@@ -1392,7 +1391,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5">
       <c r="A40" s="4" t="s">
         <v>63</v>
       </c>
@@ -1409,7 +1408,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5">
       <c r="A41" s="4" t="s">
         <v>63</v>
       </c>
@@ -1426,7 +1425,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5">
       <c r="A42" s="4" t="s">
         <v>63</v>
       </c>
@@ -1443,7 +1442,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5">
       <c r="A43" s="4" t="s">
         <v>82</v>
       </c>
@@ -1456,7 +1455,7 @@
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5">
       <c r="A44" s="4" t="s">
         <v>82</v>
       </c>
@@ -1469,7 +1468,7 @@
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5">
       <c r="A45" s="4" t="s">
         <v>82</v>
       </c>
@@ -1482,7 +1481,7 @@
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5">
       <c r="A46" s="4" t="s">
         <v>82</v>
       </c>
@@ -1495,7 +1494,7 @@
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5">
       <c r="A47" s="4" t="s">
         <v>82</v>
       </c>
@@ -1508,18 +1507,18 @@
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="17" t="s">
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C48" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
+      <c r="C48" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1540,26 +1539,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6f516c4-2602-422c-aa9a-755893ba4f98">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3c35e321-f73a-4dae-ae38-a0459de24735"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D6E01E278A50734B8A721F01C1B19487" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="03d34044917dd15f7665c3faabfa0379">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="951c5514-b77c-4532-82d5-a05f2f7d58e2" xmlns:ns3="c6f516c4-2602-422c-aa9a-755893ba4f98" xmlns:ns4="3c35e321-f73a-4dae-ae38-a0459de24735" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c6109835e45fae7978495c991aa49747" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="951c5514-b77c-4532-82d5-a05f2f7d58e2"/>
@@ -1819,33 +1798,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B84191-BBE7-412A-A5F6-7B8D27AECA6C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3c35e321-f73a-4dae-ae38-a0459de24735"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="c6f516c4-2602-422c-aa9a-755893ba4f98"/>
-    <ds:schemaRef ds:uri="951c5514-b77c-4532-82d5-a05f2f7d58e2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F0F638-0648-46BA-B1DF-3E4F6ADB00E4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6f516c4-2602-422c-aa9a-755893ba4f98">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3c35e321-f73a-4dae-ae38-a0459de24735"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{895DC2EA-9217-47D1-A436-27928D1C4E1F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1863,4 +1836,30 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F0F638-0648-46BA-B1DF-3E4F6ADB00E4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B84191-BBE7-412A-A5F6-7B8D27AECA6C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3c35e321-f73a-4dae-ae38-a0459de24735"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="c6f516c4-2602-422c-aa9a-755893ba4f98"/>
+    <ds:schemaRef ds:uri="951c5514-b77c-4532-82d5-a05f2f7d58e2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/DN - Java FSE Mandatory hands-on detail (1).xlsx
+++ b/DN - Java FSE Mandatory hands-on detail (1).xlsx
@@ -1539,6 +1539,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6f516c4-2602-422c-aa9a-755893ba4f98">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3c35e321-f73a-4dae-ae38-a0459de24735"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D6E01E278A50734B8A721F01C1B19487" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="03d34044917dd15f7665c3faabfa0379">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="951c5514-b77c-4532-82d5-a05f2f7d58e2" xmlns:ns3="c6f516c4-2602-422c-aa9a-755893ba4f98" xmlns:ns4="3c35e321-f73a-4dae-ae38-a0459de24735" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c6109835e45fae7978495c991aa49747" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="951c5514-b77c-4532-82d5-a05f2f7d58e2"/>
@@ -1798,27 +1818,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B84191-BBE7-412A-A5F6-7B8D27AECA6C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3c35e321-f73a-4dae-ae38-a0459de24735"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="c6f516c4-2602-422c-aa9a-755893ba4f98"/>
+    <ds:schemaRef ds:uri="951c5514-b77c-4532-82d5-a05f2f7d58e2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6f516c4-2602-422c-aa9a-755893ba4f98">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3c35e321-f73a-4dae-ae38-a0459de24735"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F0F638-0648-46BA-B1DF-3E4F6ADB00E4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{895DC2EA-9217-47D1-A436-27928D1C4E1F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1836,30 +1862,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F0F638-0648-46BA-B1DF-3E4F6ADB00E4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B84191-BBE7-412A-A5F6-7B8D27AECA6C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3c35e321-f73a-4dae-ae38-a0459de24735"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="c6f516c4-2602-422c-aa9a-755893ba4f98"/>
-    <ds:schemaRef ds:uri="951c5514-b77c-4532-82d5-a05f2f7d58e2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/DN - Java FSE Mandatory hands-on detail (1).xlsx
+++ b/DN - Java FSE Mandatory hands-on detail (1).xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="96">
   <si>
     <t>Skill</t>
   </si>
@@ -314,6 +314,15 @@
   </si>
   <si>
     <t>Angular Hands-on</t>
+  </si>
+  <si>
+    <t>https://github.com/Naresh-Chaurasia/GenC-React</t>
+  </si>
+  <si>
+    <t>https://github.com/Naresh-Chaurasia/GenC-KnowledgeHub/blob/main/gen-c/javascript/genc-javascript.adoc</t>
+  </si>
+  <si>
+    <t>https://github.com/Naresh-Chaurasia/GenC-KnowledgeHub</t>
   </si>
 </sst>
 </file>
@@ -838,7 +847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="23.125" customWidth="1"/>
@@ -1519,6 +1528,21 @@
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>95</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
